--- a/Backend/icnome_details.xlsx
+++ b/Backend/icnome_details.xlsx
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,51 +412,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>salary</v>
+        <v>Salary</v>
       </c>
       <c r="B2">
-        <v>20000</v>
-      </c>
-      <c r="C2" s="1">
-        <v>45689.666666666664</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>salary</v>
-      </c>
-      <c r="B3">
-        <v>30000</v>
-      </c>
-      <c r="C3" s="1">
-        <v>45689.666666666664</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>salary</v>
-      </c>
-      <c r="B4">
-        <v>40000</v>
-      </c>
-      <c r="C4" s="1">
-        <v>45689.666666666664</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>salary</v>
-      </c>
-      <c r="B5">
-        <v>50000</v>
-      </c>
-      <c r="C5" s="1">
-        <v>45689.666666666664</v>
+        <v>2000</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-02-10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Backend/icnome_details.xlsx
+++ b/Backend/icnome_details.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,18 +412,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>salary</v>
+      </c>
+      <c r="B2">
+        <v>1500</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-02-13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>Salary</v>
       </c>
-      <c r="B2">
-        <v>2000</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2026-02-10</v>
+      <c r="B3">
+        <v>500</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-02-13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>salary</v>
+      </c>
+      <c r="B4">
+        <v>500</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-02-11</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Backend/icnome_details.xlsx
+++ b/Backend/icnome_details.xlsx
@@ -397,55 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Source</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Amount</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>salary</v>
-      </c>
-      <c r="B2">
-        <v>1500</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2026-02-13</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="B3">
-        <v>500</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2026-02-13</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>salary</v>
-      </c>
-      <c r="B4">
-        <v>500</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2026-02-11</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Backend/icnome_details.xlsx
+++ b/Backend/icnome_details.xlsx
@@ -397,10 +397,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:C12"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Source</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Date</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>salary</v>
+      </c>
+      <c r="B2">
+        <v>230</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-02-24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>salary</v>
+      </c>
+      <c r="B3">
+        <v>230</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-02-24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Gift</v>
+      </c>
+      <c r="B4">
+        <v>230</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-02-23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>freelanc</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-02-23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>course</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-02-19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>salary</v>
+      </c>
+      <c r="B7">
+        <v>5000</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026-02-19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Course</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026-02-18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026-02-17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>tcs</v>
+      </c>
+      <c r="B10">
+        <v>340</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-02-17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>salary</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-02-17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Freelancer</v>
+      </c>
+      <c r="B12">
+        <v>150</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-02-16</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Backend/icnome_details.xlsx
+++ b/Backend/icnome_details.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,10 +415,10 @@
         <v>salary</v>
       </c>
       <c r="B2">
-        <v>230</v>
+        <v>5000</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-23</v>
       </c>
     </row>
     <row r="3">
@@ -426,114 +426,15 @@
         <v>salary</v>
       </c>
       <c r="B3">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-24</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Gift</v>
-      </c>
-      <c r="B4">
-        <v>230</v>
-      </c>
-      <c r="C4" t="str">
         <v>2026-02-23</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>freelanc</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2026-02-23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>course</v>
-      </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2026-02-19</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>salary</v>
-      </c>
-      <c r="B7">
-        <v>5000</v>
-      </c>
-      <c r="C7" t="str">
-        <v>2026-02-19</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Course</v>
-      </c>
-      <c r="B8">
-        <v>25</v>
-      </c>
-      <c r="C8" t="str">
-        <v>2026-02-18</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-      <c r="C9" t="str">
-        <v>2026-02-17</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>tcs</v>
-      </c>
-      <c r="B10">
-        <v>340</v>
-      </c>
-      <c r="C10" t="str">
-        <v>2026-02-17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>salary</v>
-      </c>
-      <c r="B11">
-        <v>100</v>
-      </c>
-      <c r="C11" t="str">
-        <v>2026-02-17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Freelancer</v>
-      </c>
-      <c r="B12">
-        <v>150</v>
-      </c>
-      <c r="C12" t="str">
-        <v>2026-02-16</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>